--- a/data/CDPresults.xlsx
+++ b/data/CDPresults.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\segmentation\data\mathtests\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\segmentation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B19A6A-ABC2-4F77-9BA3-C75FC71FB814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81D8210-A605-4308-9707-4C6CFF1D92ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="450" windowWidth="16665" windowHeight="14760" activeTab="1" xr2:uid="{CBDF1A6D-5BCF-4736-9138-AFBBECA9C390}"/>
+    <workbookView xWindow="32730" yWindow="135" windowWidth="23250" windowHeight="15225" activeTab="1" xr2:uid="{CBDF1A6D-5BCF-4736-9138-AFBBECA9C390}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Detail" sheetId="1" r:id="rId1"/>
     <sheet name="table" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133">
-        <f t="shared" ref="A133:A143" si="1">1+A132</f>
+        <f t="shared" ref="A133:A141" si="1">1+A132</f>
         <v>62</v>
       </c>
       <c r="B133" t="s">
